--- a/PyRrefra_variables.xlsx
+++ b/PyRrefra_variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Handbooks\Seismics\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE0B9A4-3411-49FB-AA14-79461E0970D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29315FB6-51D6-49D3-AFF6-DEC08AA09D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="6" xr2:uid="{BFEF5D69-20A1-4E9C-B635-970B36C098A9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="5" xr2:uid="{BFEF5D69-20A1-4E9C-B635-970B36C098A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="636">
   <si>
     <t>names</t>
   </si>
@@ -1893,9 +1893,6 @@
     <t>animateLine</t>
   </si>
   <si>
-    <t>Plots animation of wave evolution in time along the geophone line</t>
-  </si>
-  <si>
     <t>seg2_write</t>
   </si>
   <si>
@@ -1915,6 +1912,45 @@
   </si>
   <si>
     <t>Calculates spatial attenuation of waves using amplitude evolution</t>
+  </si>
+  <si>
+    <t>p_aim</t>
+  </si>
+  <si>
+    <t>Folder where the output of tomography results is stored</t>
+  </si>
+  <si>
+    <t>prepareSOFI2D</t>
+  </si>
+  <si>
+    <t>Writes models, shots, receivers and control (Jason format) files for SOFI2D program</t>
+  </si>
+  <si>
+    <t>Animated plot of time evolution of amplitudes of all traces to show propagation of waves</t>
+  </si>
+  <si>
+    <t>number_of_traces</t>
+  </si>
+  <si>
+    <t>total number of traces recorded (sum of traces in all files)</t>
+  </si>
+  <si>
+    <t>v_nmo</t>
+  </si>
+  <si>
+    <t>Writes NMO velocities to file v_semblance.txt for use with Seismic Unix</t>
+  </si>
+  <si>
+    <t>ffilter</t>
+  </si>
+  <si>
+    <t>Does filtering on the data of one trace</t>
+  </si>
+  <si>
+    <t>mute_before_pick</t>
+  </si>
+  <si>
+    <t>Mutes the data before and including the first-arrival source signal</t>
   </si>
 </sst>
 </file>
@@ -2271,7 +2307,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3140,7 +3176,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0718C504-98B9-497F-83D8-2E444AE76DF0}">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -3365,57 +3401,65 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>376</v>
+        <v>634</v>
       </c>
       <c r="C26" t="s">
-        <v>377</v>
+        <v>635</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>617</v>
+        <v>376</v>
       </c>
       <c r="C27" t="s">
-        <v>618</v>
+        <v>377</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>303</v>
+        <v>616</v>
       </c>
       <c r="C28" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C29" t="s">
-        <v>378</v>
+        <v>620</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>619</v>
+        <v>304</v>
       </c>
       <c r="C30" t="s">
-        <v>620</v>
+        <v>378</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>379</v>
+        <v>618</v>
       </c>
       <c r="C31" t="s">
-        <v>305</v>
+        <v>619</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>379</v>
+      </c>
+      <c r="C32" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>283</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>306</v>
       </c>
     </row>
@@ -3749,6 +3793,17 @@
         <v>191</v>
       </c>
     </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>628</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" t="s">
+        <v>629</v>
+      </c>
+    </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
@@ -3813,7 +3868,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90A6D0F4-EC08-4E13-B638-83B4548051EA}">
-  <dimension ref="A1:C94"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -4573,6 +4628,17 @@
         <v>536</v>
       </c>
     </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>623</v>
+      </c>
+      <c r="B71" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" t="s">
+        <v>624</v>
+      </c>
+    </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
@@ -4685,66 +4751,82 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>313</v>
+        <v>632</v>
       </c>
       <c r="C87" t="s">
-        <v>394</v>
+        <v>633</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C88" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C89" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C90" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>611</v>
+        <v>318</v>
       </c>
       <c r="C91" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>309</v>
+        <v>630</v>
       </c>
       <c r="C92" t="s">
-        <v>399</v>
+        <v>631</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C93" t="s">
-        <v>616</v>
+        <v>398</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>309</v>
+      </c>
+      <c r="C94" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>625</v>
+      </c>
+      <c r="C95" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>621</v>
+      </c>
+      <c r="C96" t="s">
         <v>622</v>
-      </c>
-      <c r="C94" t="s">
-        <v>623</v>
       </c>
     </row>
   </sheetData>
@@ -4757,7 +4839,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E128575D-A238-4F62-91BA-BE7AA1768365}">
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
@@ -5658,6 +5740,14 @@
         <v>371</v>
       </c>
     </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>615</v>
+      </c>
+      <c r="C104" t="s">
+        <v>627</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/PyRrefra_variables.xlsx
+++ b/PyRrefra_variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Handbooks\Seismics\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29315FB6-51D6-49D3-AFF6-DEC08AA09D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E0FFB6-5958-4F41-881E-C9B6BF45C799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="5" xr2:uid="{BFEF5D69-20A1-4E9C-B635-970B36C098A9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="8" xr2:uid="{BFEF5D69-20A1-4E9C-B635-970B36C098A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="6" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Traces" sheetId="4" r:id="rId7"/>
     <sheet name="Utilities" sheetId="7" r:id="rId8"/>
     <sheet name="Window" sheetId="5" r:id="rId9"/>
+    <sheet name="newWindow" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="654">
   <si>
     <t>names</t>
   </si>
@@ -1951,6 +1952,60 @@
   </si>
   <si>
     <t>Mutes the data before and including the first-arrival source signal</t>
+  </si>
+  <si>
+    <t>saveHeader</t>
+  </si>
+  <si>
+    <t>save all trace headers in files corresponding to the data files (headers_nnnnn.dat). Files are stored in folder ./Headers</t>
+  </si>
+  <si>
+    <t>component</t>
+  </si>
+  <si>
+    <t>Component of each trace ("Z", "V", "R", "T", "L", "N", "E")</t>
+  </si>
+  <si>
+    <t>numpy array; str</t>
+  </si>
+  <si>
+    <t>types</t>
+  </si>
+  <si>
+    <t>Components having been recorded (unique values of 5th column of file receivers.geo if it exists; if not, only "Z"</t>
+  </si>
+  <si>
+    <t>chooseComponent</t>
+  </si>
+  <si>
+    <t>Only activated if several components have been recorded (5th column of file receivers.geo), allows choosing the component to be plotted</t>
+  </si>
+  <si>
+    <t>plotComponent</t>
+  </si>
+  <si>
+    <t>Component to be plotted (if none is chosen, the values is "All")</t>
+  </si>
+  <si>
+    <t>layout</t>
+  </si>
+  <si>
+    <t>QVBoxLayout</t>
+  </si>
+  <si>
+    <t>Matplotlib Figure</t>
+  </si>
+  <si>
+    <t>canvas</t>
+  </si>
+  <si>
+    <t>Matplotlib FigureCanvas</t>
+  </si>
+  <si>
+    <t>toolbar</t>
+  </si>
+  <si>
+    <t>NavigationToolbar widget</t>
   </si>
 </sst>
 </file>
@@ -2497,6 +2552,79 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE4CB63F-334A-40AA-B12C-A75C222833C5}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.77734375" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" customWidth="1"/>
+    <col min="3" max="3" width="128" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>647</v>
+      </c>
+      <c r="B5" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>650</v>
+      </c>
+      <c r="B7" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>652</v>
+      </c>
+      <c r="B8" t="s">
+        <v>653</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD51985-3705-40E5-8FA2-EE5F297F02B6}">
   <dimension ref="A1:C24"/>
@@ -3051,7 +3179,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0FFAB86-4C0D-49FF-96DA-38662D5A2B95}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.109375" customWidth="1"/>
@@ -3116,53 +3244,64 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>641</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>640</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
       </c>
       <c r="C9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1" t="s">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>36</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C16" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3176,7 +3315,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0718C504-98B9-497F-83D8-2E444AE76DF0}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -3463,6 +3602,14 @@
         <v>306</v>
       </c>
     </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>636</v>
+      </c>
+      <c r="C34" t="s">
+        <v>637</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
@@ -3473,7 +3620,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1412E619-E253-407E-AD48-54747B1AA112}">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.88671875" customWidth="1"/>
@@ -3575,46 +3722,46 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>638</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>640</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>639</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>180</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -3625,236 +3772,247 @@
         <v>180</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>296</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>180</v>
       </c>
       <c r="C16" t="s">
-        <v>297</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B17" t="s">
-        <v>180</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>299</v>
       </c>
       <c r="B18" t="s">
         <v>180</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>537</v>
+        <v>91</v>
       </c>
       <c r="B19" t="s">
         <v>180</v>
       </c>
       <c r="C19" t="s">
-        <v>538</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>537</v>
       </c>
       <c r="B20" t="s">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>538</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s">
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B24" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>193</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>179</v>
+        <v>101</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="C25" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="B26" t="s">
-        <v>180</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B27" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C27" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B28" t="s">
         <v>181</v>
       </c>
       <c r="C28" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B29" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B30" t="s">
         <v>180</v>
       </c>
       <c r="C30" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>190</v>
+      </c>
+      <c r="B31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C31" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>628</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
         <v>2</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C32" t="s">
         <v>629</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1" t="s">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>102</v>
-      </c>
-      <c r="C35" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>176</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>298</v>
+        <v>175</v>
       </c>
       <c r="C37" t="s">
-        <v>380</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>177</v>
+        <v>298</v>
       </c>
       <c r="C38" t="s">
-        <v>178</v>
+        <v>380</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>177</v>
+      </c>
+      <c r="C39" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>294</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C40" t="s">
         <v>295</v>
       </c>
     </row>
@@ -3887,9 +4045,6 @@
       <c r="A3" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -4839,7 +4994,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E128575D-A238-4F62-91BA-BE7AA1768365}">
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:C106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
@@ -4858,9 +5013,6 @@
       <c r="A3" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -5149,602 +5301,621 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>163</v>
+        <v>645</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>156</v>
+        <v>646</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="B32" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B33" t="s">
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B34" t="s">
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B35" t="s">
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B36" t="s">
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>253</v>
+        <v>203</v>
       </c>
       <c r="B37" t="s">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>254</v>
+        <v>204</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>288</v>
+        <v>253</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>180</v>
       </c>
       <c r="C38" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>288</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>290</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>2</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C40" t="s">
         <v>291</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1" t="s">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>145</v>
-      </c>
-      <c r="C44" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C45" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C46" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>221</v>
+        <v>147</v>
       </c>
       <c r="C47" t="s">
-        <v>222</v>
+        <v>338</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C48" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>323</v>
+        <v>223</v>
       </c>
       <c r="C49" t="s">
-        <v>335</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>324</v>
+        <v>643</v>
       </c>
       <c r="C50" t="s">
-        <v>336</v>
+        <v>644</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>160</v>
+        <v>323</v>
       </c>
       <c r="C51" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>172</v>
+        <v>324</v>
       </c>
       <c r="C52" t="s">
-        <v>173</v>
+        <v>336</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>225</v>
+        <v>160</v>
       </c>
       <c r="C53" t="s">
-        <v>226</v>
+        <v>337</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>246</v>
+        <v>172</v>
       </c>
       <c r="C54" t="s">
-        <v>341</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="C55" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C56" t="s">
-        <v>250</v>
+        <v>341</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C57" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>331</v>
+        <v>249</v>
       </c>
       <c r="C58" t="s">
-        <v>342</v>
+        <v>250</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>325</v>
+        <v>251</v>
       </c>
       <c r="C59" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C60" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C61" t="s">
-        <v>608</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C62" t="s">
-        <v>609</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>606</v>
+        <v>329</v>
       </c>
       <c r="C63" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>227</v>
+        <v>330</v>
       </c>
       <c r="C64" t="s">
-        <v>229</v>
+        <v>609</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>228</v>
+        <v>606</v>
       </c>
       <c r="C65" t="s">
-        <v>343</v>
+        <v>607</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>157</v>
+        <v>227</v>
       </c>
       <c r="C66" t="s">
-        <v>344</v>
+        <v>229</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C67" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>610</v>
+        <v>157</v>
       </c>
       <c r="C68" t="s">
-        <v>231</v>
+        <v>344</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C69" t="s">
-        <v>235</v>
+        <v>345</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>233</v>
+        <v>610</v>
       </c>
       <c r="C70" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C71" t="s">
-        <v>334</v>
+        <v>235</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>614</v>
+        <v>233</v>
       </c>
       <c r="C72" t="s">
-        <v>174</v>
+        <v>236</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>168</v>
+        <v>234</v>
       </c>
       <c r="C73" t="s">
-        <v>240</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>169</v>
+        <v>614</v>
       </c>
       <c r="C74" t="s">
-        <v>241</v>
+        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C75" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C76" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C77" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C78" t="s">
-        <v>333</v>
+        <v>243</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C79" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C80" t="s">
-        <v>239</v>
+        <v>333</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>284</v>
+        <v>166</v>
       </c>
       <c r="C81" t="s">
-        <v>332</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>285</v>
+        <v>167</v>
       </c>
       <c r="C82" t="s">
-        <v>346</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>208</v>
+        <v>284</v>
       </c>
       <c r="C83" t="s">
-        <v>206</v>
+        <v>332</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="C84" t="s">
-        <v>207</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>347</v>
+        <v>208</v>
       </c>
       <c r="C85" t="s">
-        <v>348</v>
+        <v>206</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C86" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>211</v>
+        <v>347</v>
       </c>
       <c r="C87" t="s">
-        <v>212</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C88" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C89" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>613</v>
+        <v>213</v>
       </c>
       <c r="C90" t="s">
-        <v>349</v>
+        <v>216</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>350</v>
+        <v>214</v>
       </c>
       <c r="C91" t="s">
-        <v>351</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>352</v>
+        <v>613</v>
       </c>
       <c r="C92" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C93" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C94" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C95" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C96" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C97" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C98" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C99" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>217</v>
+        <v>364</v>
       </c>
       <c r="C100" t="s">
-        <v>218</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>219</v>
+        <v>365</v>
       </c>
       <c r="C101" t="s">
-        <v>220</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>368</v>
+        <v>217</v>
       </c>
       <c r="C102" t="s">
-        <v>369</v>
+        <v>218</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>370</v>
+        <v>219</v>
       </c>
       <c r="C103" t="s">
-        <v>371</v>
+        <v>220</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
+        <v>368</v>
+      </c>
+      <c r="C104" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>370</v>
+      </c>
+      <c r="C105" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>615</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C106" t="s">
         <v>627</v>
       </c>
     </row>

--- a/PyRrefra_variables.xlsx
+++ b/PyRrefra_variables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Handbooks\Seismics\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E0FFB6-5958-4F41-881E-C9B6BF45C799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB2ECA8-073C-4B70-A381-AD952C26DF38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="8" xr2:uid="{BFEF5D69-20A1-4E9C-B635-970B36C098A9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="15600" xr2:uid="{BFEF5D69-20A1-4E9C-B635-970B36C098A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="6" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="newWindow" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="672">
   <si>
     <t>names</t>
   </si>
@@ -907,9 +908,6 @@
     <t>filtered</t>
   </si>
   <si>
-    <t>True if any filter has been applied to data</t>
-  </si>
-  <si>
     <t>actual_traces</t>
   </si>
   <si>
@@ -1372,9 +1370,6 @@
     <t>Reduction velocity for de-aliasing data for velocity filtering</t>
   </si>
   <si>
-    <t>True if traces should be filtered</t>
-  </si>
-  <si>
     <t>scheme</t>
   </si>
   <si>
@@ -2006,6 +2001,66 @@
   </si>
   <si>
     <t>NavigationToolbar widget</t>
+  </si>
+  <si>
+    <t>times of all samples in a trace</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>stdev</t>
+  </si>
+  <si>
+    <t>position of all traces in actual gather (offsets or cmp coordinate)</t>
+  </si>
+  <si>
+    <t>standard deviation of amplitudes of all traces in actual gather</t>
+  </si>
+  <si>
+    <t>indeces</t>
+  </si>
+  <si>
+    <t>Numbers of traces sorted by position (x)</t>
+  </si>
+  <si>
+    <t>True if traces have been filtered</t>
+  </si>
+  <si>
+    <t>filtered_all</t>
+  </si>
+  <si>
+    <t>True if traces of all shots have been filtered</t>
+  </si>
+  <si>
+    <t>direction_start</t>
+  </si>
+  <si>
+    <t>direction_end</t>
+  </si>
+  <si>
+    <t>List of accepted geographic directions indicating the position of the beginning of a profile</t>
+  </si>
+  <si>
+    <t>List of accepted geographic directions indicating the position of the end of a profile</t>
+  </si>
+  <si>
+    <t>dir_start</t>
+  </si>
+  <si>
+    <t>geographic directions indicating the position of the beginning of a profile</t>
+  </si>
+  <si>
+    <t>dir_end</t>
+  </si>
+  <si>
+    <t>geographic directions indicating the position of the end of a profile</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>Text describing the profile used for graphics titles of seismograms qnd tomography result</t>
   </si>
 </sst>
 </file>
@@ -2370,7 +2425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F11594-9303-464D-9818-B357FD0D7B2B}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -2388,7 +2443,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2421,7 +2476,7 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2490,57 +2545,112 @@
         <v>275</v>
       </c>
     </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>662</v>
+      </c>
+      <c r="B13" t="s">
+        <v>638</v>
+      </c>
+      <c r="C13" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>663</v>
+      </c>
+      <c r="B14" t="s">
+        <v>638</v>
+      </c>
+      <c r="C14" t="s">
+        <v>665</v>
+      </c>
+    </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>19</v>
+      <c r="A15" t="s">
+        <v>666</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1" t="s">
-        <v>39</v>
+      <c r="A16" t="s">
+        <v>668</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>670</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>371</v>
+      </c>
+      <c r="C22" t="s">
         <v>372</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>256</v>
+      </c>
+      <c r="C23" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>278</v>
+      </c>
+      <c r="C24" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>280</v>
+      </c>
+      <c r="C25" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>256</v>
-      </c>
-      <c r="C18" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>278</v>
-      </c>
-      <c r="C19" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>280</v>
-      </c>
-      <c r="C20" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>281</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C26" t="s">
         <v>282</v>
       </c>
     </row>
@@ -2571,7 +2681,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2587,10 +2697,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B5" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2598,23 +2708,23 @@
         <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B8" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
   </sheetData>
@@ -2644,7 +2754,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2660,145 +2770,145 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B11" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C11" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B12" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C12" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B13" t="s">
+        <v>557</v>
+      </c>
+      <c r="C13" t="s">
         <v>559</v>
-      </c>
-      <c r="C13" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B14" t="s">
         <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>562</v>
+      </c>
+      <c r="B15" t="s">
+        <v>563</v>
+      </c>
+      <c r="C15" t="s">
         <v>564</v>
-      </c>
-      <c r="B15" t="s">
-        <v>565</v>
-      </c>
-      <c r="C15" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B16" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C16" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>567</v>
+      </c>
+      <c r="B17" t="s">
+        <v>568</v>
+      </c>
+      <c r="C17" t="s">
         <v>569</v>
-      </c>
-      <c r="B17" t="s">
-        <v>570</v>
-      </c>
-      <c r="C17" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -2817,26 +2927,26 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C22" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C23" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C24" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>
@@ -2865,7 +2975,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2881,13 +2991,13 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C5" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2898,51 +3008,51 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B7" t="s">
         <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>581</v>
+      </c>
+      <c r="B8" t="s">
+        <v>582</v>
+      </c>
+      <c r="C8" t="s">
         <v>583</v>
-      </c>
-      <c r="B8" t="s">
-        <v>584</v>
-      </c>
-      <c r="C8" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>584</v>
+      </c>
+      <c r="B9" t="s">
+        <v>585</v>
+      </c>
+      <c r="C9" t="s">
         <v>586</v>
-      </c>
-      <c r="B9" t="s">
-        <v>587</v>
-      </c>
-      <c r="C9" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -2953,51 +3063,51 @@
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>593</v>
+      </c>
+      <c r="B14" t="s">
+        <v>594</v>
+      </c>
+      <c r="C14" t="s">
         <v>595</v>
-      </c>
-      <c r="B14" t="s">
-        <v>596</v>
-      </c>
-      <c r="C14" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>596</v>
+      </c>
+      <c r="B15" t="s">
+        <v>597</v>
+      </c>
+      <c r="C15" t="s">
         <v>598</v>
-      </c>
-      <c r="B15" t="s">
-        <v>599</v>
-      </c>
-      <c r="C15" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -3016,18 +3126,18 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C20" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C21" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
   </sheetData>
@@ -3055,7 +3165,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -3195,7 +3305,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -3244,13 +3354,13 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B8" t="s">
+        <v>638</v>
+      </c>
+      <c r="C8" t="s">
         <v>640</v>
-      </c>
-      <c r="C8" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -3315,7 +3425,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0718C504-98B9-497F-83D8-2E444AE76DF0}">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -3332,7 +3442,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -3480,86 +3590,83 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>180</v>
       </c>
       <c r="C17" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
         <v>292</v>
       </c>
-      <c r="B18" t="s">
-        <v>180</v>
-      </c>
-      <c r="C18" t="s">
-        <v>293</v>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1" t="s">
-        <v>39</v>
+      <c r="A22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>632</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>633</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>634</v>
+        <v>375</v>
       </c>
       <c r="C26" t="s">
-        <v>635</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>376</v>
+        <v>614</v>
       </c>
       <c r="C27" t="s">
-        <v>377</v>
+        <v>615</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>616</v>
+        <v>302</v>
       </c>
       <c r="C28" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -3567,28 +3674,28 @@
         <v>303</v>
       </c>
       <c r="C29" t="s">
-        <v>620</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>304</v>
+        <v>616</v>
       </c>
       <c r="C30" t="s">
-        <v>378</v>
+        <v>617</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>618</v>
+        <v>378</v>
       </c>
       <c r="C31" t="s">
-        <v>619</v>
+        <v>304</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>379</v>
+        <v>283</v>
       </c>
       <c r="C32" t="s">
         <v>305</v>
@@ -3596,18 +3703,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>283</v>
+        <v>634</v>
       </c>
       <c r="C33" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>636</v>
-      </c>
-      <c r="C34" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
   </sheetData>
@@ -3637,7 +3736,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C3" t="s">
         <v>72</v>
@@ -3667,13 +3766,13 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B6" t="s">
         <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -3722,13 +3821,13 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>636</v>
+      </c>
+      <c r="B11" t="s">
         <v>638</v>
       </c>
-      <c r="B11" t="s">
-        <v>640</v>
-      </c>
       <c r="C11" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -3788,24 +3887,24 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B18" t="s">
         <v>180</v>
       </c>
       <c r="C18" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -3821,13 +3920,13 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B20" t="s">
         <v>180</v>
       </c>
       <c r="C20" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -3953,13 +4052,13 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B32" t="s">
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -3994,10 +4093,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C38" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -4010,10 +4109,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>293</v>
+      </c>
+      <c r="C40" t="s">
         <v>294</v>
-      </c>
-      <c r="C40" t="s">
-        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -4026,7 +4125,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90A6D0F4-EC08-4E13-B638-83B4548051EA}">
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -4043,7 +4142,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -4059,178 +4158,178 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B5" t="s">
         <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B7" t="s">
         <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B8" t="s">
         <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B9" t="s">
         <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B10" t="s">
         <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B11" t="s">
         <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B12" t="s">
         <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B15" t="s">
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -4241,180 +4340,180 @@
         <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>442</v>
+        <v>659</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>432</v>
+        <v>660</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>433</v>
+        <v>661</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B27" t="s">
-        <v>444</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B28" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C28" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B29" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C29" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B30" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C30" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B31" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C31" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>445</v>
       </c>
       <c r="C32" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B33" t="s">
         <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B34" t="s">
         <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B35" t="s">
         <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B36" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C36" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C37" t="s">
         <v>463</v>
@@ -4422,446 +4521,449 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B38" t="s">
         <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="B39" t="s">
         <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B40" t="s">
         <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B41" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B42" t="s">
-        <v>476</v>
+        <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B43" t="s">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="C43" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B44" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C44" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B45" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C45" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>122</v>
+        <v>480</v>
       </c>
       <c r="B46" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C46" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="B47" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C47" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>445</v>
       </c>
       <c r="C48" t="s">
-        <v>504</v>
+        <v>484</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B49" t="s">
         <v>26</v>
       </c>
       <c r="C49" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B50" t="s">
         <v>26</v>
       </c>
       <c r="C50" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B51" t="s">
         <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B52" t="s">
         <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B53" t="s">
         <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B54" t="s">
         <v>26</v>
       </c>
       <c r="C54" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B55" t="s">
         <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B56" t="s">
         <v>26</v>
       </c>
       <c r="C56" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B57" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C57" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B58" t="s">
-        <v>502</v>
+        <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="B59" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="C59" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B60" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C60" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="B61" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C61" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="B62" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C62" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B63" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C63" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B64" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C64" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B65" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C65" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B66" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C66" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="B67" t="s">
-        <v>26</v>
+        <v>515</v>
       </c>
       <c r="C67" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B68" t="s">
         <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B69" t="s">
-        <v>447</v>
+        <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B70" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C70" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>623</v>
+        <v>530</v>
       </c>
       <c r="B71" t="s">
+        <v>445</v>
+      </c>
+      <c r="C71" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>621</v>
+      </c>
+      <c r="B72" t="s">
         <v>8</v>
       </c>
-      <c r="C71" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
-        <v>19</v>
+      <c r="C72" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1" t="s">
+      <c r="B75" s="1"/>
+      <c r="C75" s="1" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>294</v>
-      </c>
-      <c r="C75" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="C76" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>612</v>
+        <v>306</v>
       </c>
       <c r="C77" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>308</v>
+        <v>610</v>
       </c>
       <c r="C78" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="C79" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C80" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C81" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -4869,36 +4971,36 @@
         <v>319</v>
       </c>
       <c r="C82" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>381</v>
+        <v>318</v>
       </c>
       <c r="C83" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>310</v>
+        <v>380</v>
       </c>
       <c r="C84" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C85" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C86" t="s">
         <v>392</v>
@@ -4906,82 +5008,90 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>632</v>
+        <v>311</v>
       </c>
       <c r="C87" t="s">
-        <v>633</v>
+        <v>391</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>313</v>
+        <v>630</v>
       </c>
       <c r="C88" t="s">
-        <v>394</v>
+        <v>631</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C89" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C90" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C91" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>630</v>
+        <v>317</v>
       </c>
       <c r="C92" t="s">
-        <v>631</v>
+        <v>396</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>611</v>
+        <v>628</v>
       </c>
       <c r="C93" t="s">
-        <v>398</v>
+        <v>629</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>309</v>
+        <v>609</v>
       </c>
       <c r="C94" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>625</v>
+        <v>308</v>
       </c>
       <c r="C95" t="s">
-        <v>626</v>
+        <v>398</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C96" t="s">
-        <v>622</v>
+        <v>624</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>619</v>
+      </c>
+      <c r="C97" t="s">
+        <v>620</v>
       </c>
     </row>
   </sheetData>
@@ -4994,7 +5104,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E128575D-A238-4F62-91BA-BE7AA1768365}">
-  <dimension ref="A1:C106"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
@@ -5011,7 +5121,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -5085,10 +5195,10 @@
         <v>154</v>
       </c>
       <c r="B10" t="s">
+        <v>313</v>
+      </c>
+      <c r="C10" t="s">
         <v>314</v>
-      </c>
-      <c r="C10" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -5301,13 +5411,13 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -5389,190 +5499,202 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>180</v>
       </c>
       <c r="C39" t="s">
-        <v>289</v>
+        <v>652</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>653</v>
+      </c>
+      <c r="B40" t="s">
+        <v>180</v>
+      </c>
+      <c r="C40" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>654</v>
+      </c>
+      <c r="B41" t="s">
+        <v>180</v>
+      </c>
+      <c r="C41" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>287</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>289</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" t="s">
         <v>290</v>
       </c>
-      <c r="B40" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>657</v>
+      </c>
+      <c r="B44" t="s">
+        <v>181</v>
+      </c>
+      <c r="C44" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1" t="s">
+      <c r="B48" s="1"/>
+      <c r="C48" s="1" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>145</v>
-      </c>
-      <c r="C45" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>146</v>
-      </c>
-      <c r="C46" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>147</v>
-      </c>
-      <c r="C47" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>221</v>
-      </c>
-      <c r="C48" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>223</v>
+        <v>145</v>
       </c>
       <c r="C49" t="s">
-        <v>224</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>643</v>
+        <v>146</v>
       </c>
       <c r="C50" t="s">
-        <v>644</v>
+        <v>339</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>323</v>
+        <v>147</v>
       </c>
       <c r="C51" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>324</v>
+        <v>221</v>
       </c>
       <c r="C52" t="s">
-        <v>336</v>
+        <v>222</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="C53" t="s">
-        <v>337</v>
+        <v>224</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>172</v>
+        <v>641</v>
       </c>
       <c r="C54" t="s">
-        <v>173</v>
+        <v>642</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>225</v>
+        <v>322</v>
       </c>
       <c r="C55" t="s">
-        <v>226</v>
+        <v>334</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>246</v>
+        <v>323</v>
       </c>
       <c r="C56" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>247</v>
+        <v>160</v>
       </c>
       <c r="C57" t="s">
-        <v>248</v>
+        <v>336</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>249</v>
+        <v>172</v>
       </c>
       <c r="C58" t="s">
-        <v>250</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="C59" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>331</v>
+        <v>246</v>
       </c>
       <c r="C60" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>325</v>
+        <v>247</v>
       </c>
       <c r="C61" t="s">
-        <v>326</v>
+        <v>248</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>327</v>
+        <v>249</v>
       </c>
       <c r="C62" t="s">
-        <v>328</v>
+        <v>250</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>329</v>
+        <v>251</v>
       </c>
       <c r="C63" t="s">
-        <v>608</v>
+        <v>252</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -5580,343 +5702,375 @@
         <v>330</v>
       </c>
       <c r="C64" t="s">
-        <v>609</v>
+        <v>341</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>606</v>
+        <v>324</v>
       </c>
       <c r="C65" t="s">
-        <v>607</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>227</v>
+        <v>326</v>
       </c>
       <c r="C66" t="s">
-        <v>229</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>228</v>
+        <v>328</v>
       </c>
       <c r="C67" t="s">
-        <v>343</v>
+        <v>606</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>157</v>
+        <v>329</v>
       </c>
       <c r="C68" t="s">
-        <v>344</v>
+        <v>607</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>230</v>
+        <v>604</v>
       </c>
       <c r="C69" t="s">
-        <v>345</v>
+        <v>605</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>610</v>
+        <v>227</v>
       </c>
       <c r="C70" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C71" t="s">
-        <v>235</v>
+        <v>342</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>233</v>
+        <v>157</v>
       </c>
       <c r="C72" t="s">
-        <v>236</v>
+        <v>343</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C73" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="C74" t="s">
-        <v>174</v>
+        <v>231</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>168</v>
+        <v>232</v>
       </c>
       <c r="C75" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>169</v>
+        <v>233</v>
       </c>
       <c r="C76" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>170</v>
+        <v>234</v>
       </c>
       <c r="C77" t="s">
-        <v>242</v>
+        <v>333</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>171</v>
+        <v>612</v>
       </c>
       <c r="C78" t="s">
-        <v>243</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C79" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C80" t="s">
-        <v>333</v>
+        <v>241</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C81" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C82" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>284</v>
+        <v>165</v>
       </c>
       <c r="C83" t="s">
-        <v>332</v>
+        <v>237</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>285</v>
+        <v>164</v>
       </c>
       <c r="C84" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>208</v>
+        <v>166</v>
       </c>
       <c r="C85" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="C86" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>347</v>
+        <v>284</v>
       </c>
       <c r="C87" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>209</v>
+        <v>285</v>
       </c>
       <c r="C88" t="s">
-        <v>210</v>
+        <v>345</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C89" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C90" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>214</v>
+        <v>346</v>
       </c>
       <c r="C91" t="s">
-        <v>215</v>
+        <v>347</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>613</v>
+        <v>209</v>
       </c>
       <c r="C92" t="s">
-        <v>349</v>
+        <v>210</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>350</v>
+        <v>211</v>
       </c>
       <c r="C93" t="s">
-        <v>351</v>
+        <v>212</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>352</v>
+        <v>213</v>
       </c>
       <c r="C94" t="s">
-        <v>353</v>
+        <v>216</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>354</v>
+        <v>214</v>
       </c>
       <c r="C95" t="s">
-        <v>355</v>
+        <v>215</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>356</v>
+        <v>611</v>
       </c>
       <c r="C96" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C97" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C98" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C99" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C100" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C101" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>217</v>
+        <v>359</v>
       </c>
       <c r="C102" t="s">
-        <v>218</v>
+        <v>360</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>219</v>
+        <v>361</v>
       </c>
       <c r="C103" t="s">
-        <v>220</v>
+        <v>362</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C104" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="C105" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>615</v>
+        <v>217</v>
       </c>
       <c r="C106" t="s">
-        <v>627</v>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>219</v>
+      </c>
+      <c r="C107" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>367</v>
+      </c>
+      <c r="C108" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>369</v>
+      </c>
+      <c r="C109" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>613</v>
+      </c>
+      <c r="C110" t="s">
+        <v>625</v>
       </c>
     </row>
   </sheetData>
